--- a/apps/saucedemo/test-cases/saucedemo_test_cases.xlsx
+++ b/apps/saucedemo/test-cases/saucedemo_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="292">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -70,13 +70,13 @@
 Click Login</t>
   </si>
   <si>
-    <t>User should be redirected to the inventory page and the Products title should be displayed</t>
+    <t>User should be successfully logged in and redirected to the inventory page</t>
   </si>
   <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>Use stable data-test selectors such as username, password, login-button, and title</t>
+    <t>Use data-test selectors: username, password, login-button</t>
   </si>
   <si>
     <t>LoginPage</t>
@@ -91,16 +91,16 @@
     <t>Negative</t>
   </si>
   <si>
-    <t xml:space="preserve">Navigate to https://www.saucedemo.com/
+    <t xml:space="preserve">Navigate to application
 Enter username locked_out_user
 Enter password secret_sauce
 Click Login</t>
   </si>
   <si>
-    <t>User should remain on the login page and error message 'Epic sadface: Sorry, this user has been locked out.' should be displayed</t>
-  </si>
-  <si>
-    <t>Use data-test selectors username, password, login-button, and error</t>
+    <t>User should remain on the login page and an error message should display indicating the user has been locked out</t>
+  </si>
+  <si>
+    <t>Use data-test selectors: username, password, login-button, error</t>
   </si>
   <si>
     <t>TC_LOGIN_003</t>
@@ -109,13 +109,13 @@
     <t>Login with invalid username and valid password</t>
   </si>
   <si>
-    <t xml:space="preserve">Navigate to https://www.saucedemo.com/
-Enter username invalid_user
+    <t xml:space="preserve">Navigate to application
+Enter an invalid username
 Enter password secret_sauce
 Click Login</t>
   </si>
   <si>
-    <t>User should remain on the login page and error message 'Epic sadface: Username and password do not match any user in this service' should be displayed</t>
+    <t>User should not be logged in and an error message should indicate username and password do not match any user</t>
   </si>
   <si>
     <t>TC_LOGIN_004</t>
@@ -124,144 +124,89 @@
     <t>Login with valid username and invalid password</t>
   </si>
   <si>
-    <t xml:space="preserve">Navigate to https://www.saucedemo.com/
+    <t xml:space="preserve">Navigate to application
 Enter username standard_user
-Enter password invalid_password
+Enter an invalid password
 Click Login</t>
   </si>
   <si>
-    <t>User should remain on the login page and invalid credentials error should be displayed</t>
-  </si>
-  <si>
     <t>TC_LOGIN_005</t>
   </si>
   <si>
-    <t>Login with blank username and blank password</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navigate to https://www.saucedemo.com/
-Leave username field blank
-Leave password field blank
+    <t>Login with empty username and password</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navigate to application
+Leave username field empty
+Leave password field empty
 Click Login</t>
   </si>
   <si>
-    <t>User should remain on the login page and error message 'Epic sadface: Username is required' should be displayed</t>
-  </si>
-  <si>
-    <t>Use data-test selectors login-button and error</t>
+    <t>User should not be logged in and an error message should indicate username is required</t>
+  </si>
+  <si>
+    <t>Use data-test selectors: login-button, error</t>
   </si>
   <si>
     <t>TC_LOGIN_006</t>
   </si>
   <si>
-    <t>Login with username only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navigate to https://www.saucedemo.com/
+    <t>Login with empty password</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navigate to application
 Enter username standard_user
-Leave password field blank
+Leave password field empty
 Click Login</t>
   </si>
   <si>
-    <t>User should remain on the login page and error message 'Epic sadface: Password is required' should be displayed</t>
-  </si>
-  <si>
-    <t>Use data-test selectors username, login-button, and error</t>
+    <t>User should not be logged in and an error message should indicate password is required</t>
+  </si>
+  <si>
+    <t>Use data-test selectors: username, login-button, error</t>
   </si>
   <si>
     <t>TC_LOGIN_007</t>
   </si>
   <si>
-    <t>Login with password only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navigate to https://www.saucedemo.com/
-Leave username field blank
-Enter password secret_sauce
-Click Login</t>
-  </si>
-  <si>
-    <t>Use data-test selectors password, login-button, and error</t>
-  </si>
-  <si>
-    <t>TC_LOGIN_008</t>
-  </si>
-  <si>
-    <t>Verify error message can be dismissed</t>
+    <t>Login with leading and trailing spaces in credentials</t>
+  </si>
+  <si>
+    <t>Edge</t>
   </si>
   <si>
     <t>Medium</t>
   </si>
   <si>
-    <t>User is on the login page and an error message is displayed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trigger a login validation error
-Click the error close button</t>
-  </si>
-  <si>
-    <t>Error message should be dismissed from the login page</t>
-  </si>
-  <si>
-    <t>Use data-test selector error-button for closing the error</t>
-  </si>
-  <si>
-    <t>TC_LOGIN_009</t>
-  </si>
-  <si>
-    <t>Access inventory page directly without authentication</t>
-  </si>
-  <si>
-    <t>User is not logged in</t>
-  </si>
-  <si>
-    <t>Navigate directly to https://www.saucedemo.com/inventory.html</t>
-  </si>
-  <si>
-    <t>User should be redirected to the login page and error message should indicate authentication is required</t>
-  </si>
-  <si>
-    <t>Validate current URL and use data-test selector error</t>
-  </si>
-  <si>
-    <t>TC_LOGIN_010</t>
-  </si>
-  <si>
-    <t>Logout after successful login</t>
-  </si>
-  <si>
-    <t>User is logged in as standard_user and is on the inventory page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click the burger menu button
-Click Logout</t>
-  </si>
-  <si>
-    <t>User should be logged out and redirected to the login page</t>
-  </si>
-  <si>
-    <t>Use data-test selectors open-menu, logout-sidebar-link, and login-button</t>
-  </si>
-  <si>
-    <t>InventoryPage</t>
-  </si>
-  <si>
-    <t>TC_LOGIN_011</t>
-  </si>
-  <si>
-    <t>Login with leading and trailing spaces in username</t>
-  </si>
-  <si>
-    <t>Edge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navigate to https://www.saucedemo.com/
+    <t xml:space="preserve">Navigate to application
 Enter username with leading and trailing spaces around standard_user
 Enter password secret_sauce
 Click Login</t>
   </si>
   <si>
-    <t>Login should fail unless the application intentionally trims input; invalid credentials error should be displayed</t>
+    <t>User should not be logged in unless the application explicitly trims whitespace; error behavior should be consistent and user-friendly</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_008</t>
+  </si>
+  <si>
+    <t>Verify logout returns user to login page</t>
+  </si>
+  <si>
+    <t>User is logged in as standard_user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Click the burger menu
+Click Logout</t>
+  </si>
+  <si>
+    <t>User should be logged out and redirected to the login page</t>
+  </si>
+  <si>
+    <t>Use data-test selectors: open-menu, logout-sidebar-link</t>
+  </si>
+  <si>
+    <t>InventoryPage</t>
   </si>
   <si>
     <t>TC_INVENTORY_001</t>
@@ -270,184 +215,172 @@
     <t>Inventory</t>
   </si>
   <si>
-    <t>Verify inventory page loads all products</t>
-  </si>
-  <si>
-    <t>User is logged in as standard_user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navigate to the inventory page
-Count the displayed inventory items</t>
-  </si>
-  <si>
-    <t>Inventory page should display 6 products with product names, descriptions, prices, images, and Add to cart buttons</t>
-  </si>
-  <si>
-    <t>Use data-test selectors inventory-item, inventory-item-name, inventory-item-desc, inventory-item-price, and add-to-cart buttons</t>
+    <t>Verify inventory page loads after successful login</t>
+  </si>
+  <si>
+    <t>User has valid credentials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log in as standard_user
+Observe inventory page header and product list</t>
+  </si>
+  <si>
+    <t>Inventory page should display the Products title, product cards, cart icon, menu button, and sorting dropdown</t>
+  </si>
+  <si>
+    <t>Use data-test selectors: title, inventory-list, shopping-cart-link, product-sort-container</t>
   </si>
   <si>
     <t>TC_INVENTORY_002</t>
   </si>
   <si>
-    <t>Add a product to cart from inventory page</t>
-  </si>
-  <si>
-    <t>User is logged in as standard_user and cart is empty</t>
-  </si>
-  <si>
-    <t>Click Add to cart for Sauce Labs Backpack</t>
-  </si>
-  <si>
-    <t>Button should change to Remove and cart badge should display 1</t>
-  </si>
-  <si>
-    <t>Use data-test selectors add-to-cart-sauce-labs-backpack, remove-sauce-labs-backpack, and shopping-cart-badge</t>
+    <t>Verify all expected products are displayed</t>
+  </si>
+  <si>
+    <t>User is logged in and on inventory page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load inventory page
+Capture displayed product names
+Compare product names with expected inventory items</t>
+  </si>
+  <si>
+    <t>All expected SauceDemo products should be displayed with name, description, price, image, and Add to cart button</t>
+  </si>
+  <si>
+    <t>Use data-test selectors: inventory-item, inventory-item-name, inventory-item-desc, inventory-item-price</t>
   </si>
   <si>
     <t>TC_INVENTORY_003</t>
   </si>
   <si>
-    <t>Remove a product from inventory page</t>
-  </si>
-  <si>
-    <t>User is logged in and Sauce Labs Backpack is already added to cart</t>
-  </si>
-  <si>
-    <t>Click Remove for Sauce Labs Backpack</t>
-  </si>
-  <si>
-    <t>Product should be removed from cart, button should change to Add to cart, and cart badge should be removed or decremented</t>
-  </si>
-  <si>
-    <t>Use data-test selectors remove-sauce-labs-backpack, add-to-cart-sauce-labs-backpack, and shopping-cart-badge</t>
+    <t>Sort products by name A to Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open the sort dropdown
+Select Name A to Z
+Capture displayed product names</t>
+  </si>
+  <si>
+    <t>Products should be sorted alphabetically from A to Z</t>
+  </si>
+  <si>
+    <t>Use data-test selector: product-sort-container and inventory-item-name</t>
   </si>
   <si>
     <t>TC_INVENTORY_004</t>
   </si>
   <si>
-    <t>Open product detail page from inventory item name</t>
-  </si>
-  <si>
-    <t>Click the product name Sauce Labs Backpack</t>
-  </si>
-  <si>
-    <t>Product detail page should open and show matching product name, description, price, and image</t>
-  </si>
-  <si>
-    <t>Use data-test selector item-4-title-link and product detail selectors inventory-item-name, inventory-item-desc, inventory-item-price</t>
+    <t>Sort products by name Z to A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open the sort dropdown
+Select Name Z to A
+Capture displayed product names</t>
+  </si>
+  <si>
+    <t>Products should be sorted alphabetically from Z to A</t>
   </si>
   <si>
     <t>TC_INVENTORY_005</t>
   </si>
   <si>
-    <t>Navigate back from product detail page to inventory</t>
-  </si>
-  <si>
-    <t>User is logged in and is on a product detail page</t>
-  </si>
-  <si>
-    <t>Click Back to products</t>
-  </si>
-  <si>
-    <t>User should return to inventory page and Products title should be displayed</t>
-  </si>
-  <si>
-    <t>Use data-test selector back-to-products and title</t>
-  </si>
-  <si>
-    <t>ProductDetailPage</t>
+    <t>Sort products by price low to high</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open the sort dropdown
+Select Price low to high
+Capture displayed product prices</t>
+  </si>
+  <si>
+    <t>Products should be sorted by price in ascending order</t>
+  </si>
+  <si>
+    <t>Use data-test selector: product-sort-container and inventory-item-price</t>
   </si>
   <si>
     <t>TC_INVENTORY_006</t>
   </si>
   <si>
-    <t>Sort products by name ascending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open product sort dropdown
-Select Name A to Z</t>
-  </si>
-  <si>
-    <t>Products should be sorted alphabetically from A to Z by product name</t>
-  </si>
-  <si>
-    <t>Use data-test selector product-sort-container and inventory-item-name</t>
+    <t>Sort products by price high to low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open the sort dropdown
+Select Price high to low
+Capture displayed product prices</t>
+  </si>
+  <si>
+    <t>Products should be sorted by price in descending order</t>
   </si>
   <si>
     <t>TC_INVENTORY_007</t>
   </si>
   <si>
-    <t>Sort products by name descending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open product sort dropdown
-Select Name Z to A</t>
-  </si>
-  <si>
-    <t>Products should be sorted alphabetically from Z to A by product name</t>
+    <t>Open product details from inventory item name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Click a product name
+Observe product detail page</t>
+  </si>
+  <si>
+    <t>Product detail page should display matching product name, description, price, image, Add to cart button, and Back to products button</t>
+  </si>
+  <si>
+    <t>Use data-test selectors: inventory-item-name, inventory-details-name, inventory-details-price, back-to-products</t>
+  </si>
+  <si>
+    <t>ProductDetailsPage</t>
   </si>
   <si>
     <t>TC_INVENTORY_008</t>
   </si>
   <si>
-    <t>Sort products by price low to high</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open product sort dropdown
-Select Price low to high</t>
-  </si>
-  <si>
-    <t>Products should be sorted by price in ascending order</t>
-  </si>
-  <si>
-    <t>Use data-test selector product-sort-container and inventory-item-price</t>
+    <t>Add single product to cart from inventory page</t>
+  </si>
+  <si>
+    <t>Click Add to cart for one product</t>
+  </si>
+  <si>
+    <t>Cart badge should show 1 and product button should change to Remove</t>
+  </si>
+  <si>
+    <t>Use data-test selectors for product add button, remove button, and shopping-cart-badge</t>
   </si>
   <si>
     <t>TC_INVENTORY_009</t>
   </si>
   <si>
-    <t>Sort products by price high to low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open product sort dropdown
-Select Price high to low</t>
-  </si>
-  <si>
-    <t>Products should be sorted by price in descending order</t>
+    <t>Remove product from inventory page after adding it</t>
+  </si>
+  <si>
+    <t>User is logged in and has added one product to cart</t>
+  </si>
+  <si>
+    <t>Click Remove for the added product</t>
+  </si>
+  <si>
+    <t>Cart badge should be removed or decremented and product button should change back to Add to cart</t>
+  </si>
+  <si>
+    <t>Use data-test selectors for product remove button and shopping-cart-badge</t>
   </si>
   <si>
     <t>TC_INVENTORY_010</t>
   </si>
   <si>
-    <t>Add all products to cart</t>
-  </si>
-  <si>
-    <t>Click Add to cart for each product displayed on the inventory page</t>
-  </si>
-  <si>
-    <t>All product buttons should change to Remove and cart badge should display 6</t>
-  </si>
-  <si>
-    <t>Use data-test selectors for all add-to-cart buttons and shopping-cart-badge</t>
-  </si>
-  <si>
-    <t>TC_INVENTORY_011</t>
-  </si>
-  <si>
-    <t>Reset app state from menu</t>
-  </si>
-  <si>
-    <t>User is logged in and has one or more items in the cart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click the burger menu button
-Click Reset App State</t>
-  </si>
-  <si>
-    <t>Cart should be cleared, cart badge should disappear, and product buttons should show Add to cart</t>
-  </si>
-  <si>
-    <t>Use data-test selectors open-menu, reset-sidebar-link, shopping-cart-badge, and add-to-cart buttons</t>
+    <t>Verify inventory page cannot be accessed without authentication</t>
+  </si>
+  <si>
+    <t>User is not logged in</t>
+  </si>
+  <si>
+    <t>Navigate directly to https://www.saucedemo.com/inventory.html</t>
+  </si>
+  <si>
+    <t>User should be redirected to login page and an error message should indicate authentication is required</t>
+  </si>
+  <si>
+    <t>Use URL assertion and data-test selector: error</t>
   </si>
   <si>
     <t>TC_CART_001</t>
@@ -456,124 +389,158 @@
     <t>Cart</t>
   </si>
   <si>
-    <t>Open cart from inventory page</t>
-  </si>
-  <si>
-    <t>Click the shopping cart icon</t>
-  </si>
-  <si>
-    <t>User should be redirected to the cart page and Your Cart title should be displayed</t>
-  </si>
-  <si>
-    <t>Use data-test selector shopping-cart-link and title</t>
+    <t>Add multiple products to cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Click Add to cart for two or more products
+Observe cart badge</t>
+  </si>
+  <si>
+    <t>Cart badge should display the correct number of added products</t>
+  </si>
+  <si>
+    <t>Use data-test selectors for add-to-cart buttons and shopping-cart-badge</t>
+  </si>
+  <si>
+    <t>TC_CART_002</t>
+  </si>
+  <si>
+    <t>Navigate to cart from inventory page</t>
+  </si>
+  <si>
+    <t>User is logged in and has added at least one product to cart</t>
+  </si>
+  <si>
+    <t>Click the cart icon</t>
+  </si>
+  <si>
+    <t>User should be navigated to the cart page and added products should be displayed</t>
+  </si>
+  <si>
+    <t>Use data-test selector: shopping-cart-link, inventory-item-name</t>
   </si>
   <si>
     <t>CartPage</t>
   </si>
   <si>
-    <t>TC_CART_002</t>
-  </si>
-  <si>
-    <t>Verify added item appears in cart</t>
-  </si>
-  <si>
-    <t>User is logged in and Sauce Labs Backpack is added to cart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click the shopping cart icon
-Review the cart item details</t>
-  </si>
-  <si>
-    <t>Cart should display Sauce Labs Backpack with correct quantity, name, description, and price</t>
-  </si>
-  <si>
-    <t>Use data-test selectors inventory-item-name, inventory-item-desc, inventory-item-price, and item-quantity</t>
-  </si>
-  <si>
     <t>TC_CART_003</t>
   </si>
   <si>
-    <t>Remove item from cart page</t>
-  </si>
-  <si>
-    <t>User is logged in and one item is present in the cart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navigate to the cart page
-Click Remove for the item</t>
-  </si>
-  <si>
-    <t>Item should be removed from cart and cart badge should be removed or decremented</t>
-  </si>
-  <si>
-    <t>Use data-test selectors remove-sauce-labs-backpack and shopping-cart-badge</t>
+    <t>Verify cart item details match inventory item details</t>
+  </si>
+  <si>
+    <t>User is logged in and has added a product to cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capture product name, description, and price from inventory page
+Open cart
+Compare cart item details with captured inventory details</t>
+  </si>
+  <si>
+    <t>Cart item name, description, and price should match the selected inventory product</t>
+  </si>
+  <si>
+    <t>Use data-test selectors: inventory-item-name, inventory-item-desc, inventory-item-price</t>
   </si>
   <si>
     <t>TC_CART_004</t>
   </si>
   <si>
+    <t>Remove product from cart page</t>
+  </si>
+  <si>
+    <t>User is logged in and has at least one product in cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open cart page
+Click Remove for a cart item</t>
+  </si>
+  <si>
+    <t>Product should be removed from the cart and cart badge should update accordingly</t>
+  </si>
+  <si>
+    <t>Use data-test selectors for remove buttons and shopping-cart-badge</t>
+  </si>
+  <si>
+    <t>TC_CART_005</t>
+  </si>
+  <si>
     <t>Continue shopping from cart page</t>
   </si>
   <si>
-    <t>User is logged in and is on the cart page</t>
+    <t>User is logged in and on cart page</t>
   </si>
   <si>
     <t>Click Continue Shopping</t>
   </si>
   <si>
-    <t>User should be redirected to the inventory page</t>
-  </si>
-  <si>
-    <t>Use data-test selector continue-shopping and title</t>
-  </si>
-  <si>
-    <t>TC_CART_005</t>
-  </si>
-  <si>
-    <t>Proceed to checkout with item in cart</t>
-  </si>
-  <si>
-    <t>User is logged in and at least one item is present in the cart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navigate to the cart page
+    <t>User should be navigated back to the inventory page</t>
+  </si>
+  <si>
+    <t>Use data-test selector: continue-shopping</t>
+  </si>
+  <si>
+    <t>TC_CART_006</t>
+  </si>
+  <si>
+    <t>Open cart with no items</t>
+  </si>
+  <si>
+    <t>User is logged in and cart is empty</t>
+  </si>
+  <si>
+    <t>Cart page should open with no cart items displayed and no cart badge count</t>
+  </si>
+  <si>
+    <t>Use data-test selector: shopping-cart-link and inventory-item</t>
+  </si>
+  <si>
+    <t>TC_CART_007</t>
+  </si>
+  <si>
+    <t>Verify cart contents persist after page refresh</t>
+  </si>
+  <si>
+    <t>User is logged in and has added products to cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open cart page
+Refresh the browser
+Observe cart contents and badge</t>
+  </si>
+  <si>
+    <t>Cart contents and badge count should persist after refresh</t>
+  </si>
+  <si>
+    <t>Use data-test selectors: shopping-cart-badge, inventory-item-name</t>
+  </si>
+  <si>
+    <t>TC_CHECKOUT_001</t>
+  </si>
+  <si>
+    <t>Checkout</t>
+  </si>
+  <si>
+    <t>Start checkout from cart with product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open cart page
 Click Checkout</t>
   </si>
   <si>
-    <t>User should be redirected to checkout step one page</t>
-  </si>
-  <si>
-    <t>Use data-test selectors checkout and title</t>
-  </si>
-  <si>
-    <t>TC_CART_006</t>
-  </si>
-  <si>
-    <t>Proceed to checkout with empty cart</t>
-  </si>
-  <si>
-    <t>User is logged in and cart is empty</t>
-  </si>
-  <si>
-    <t>Application behavior should be validated; ideally user should not proceed with empty cart or should see an appropriate validation message</t>
-  </si>
-  <si>
-    <t>Use data-test selectors checkout, cart-list, and title</t>
-  </si>
-  <si>
-    <t>TC_CHECKOUT_001</t>
-  </si>
-  <si>
-    <t>Checkout</t>
-  </si>
-  <si>
-    <t>Complete checkout successfully with valid customer information</t>
-  </si>
-  <si>
-    <t>User is logged in and has at least one item in cart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navigate to cart page
+    <t>User should be navigated to the checkout information page</t>
+  </si>
+  <si>
+    <t>Use data-test selector: checkout</t>
+  </si>
+  <si>
+    <t>TC_CHECKOUT_002</t>
+  </si>
+  <si>
+    <t>Complete checkout with valid customer information</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open cart page
 Click Checkout
 Enter first name John
 Enter last name Doe
@@ -582,226 +549,230 @@
 Click Finish</t>
   </si>
   <si>
-    <t>Order should be completed and confirmation message 'Thank you for your order!' should be displayed</t>
-  </si>
-  <si>
-    <t>Use data-test selectors firstName, lastName, postalCode, continue, finish, complete-header</t>
+    <t>Checkout should complete successfully and order confirmation page should display</t>
+  </si>
+  <si>
+    <t>Use data-test selectors: checkout, firstName, lastName, postalCode, continue, finish, complete-header</t>
   </si>
   <si>
     <t>CheckoutPage</t>
   </si>
   <si>
-    <t>TC_CHECKOUT_002</t>
-  </si>
-  <si>
-    <t>Checkout step one with valid customer information</t>
-  </si>
-  <si>
-    <t>User is logged in, has an item in cart, and is on checkout step one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enter first name John
+    <t>TC_CHECKOUT_003</t>
+  </si>
+  <si>
+    <t>Verify checkout overview totals</t>
+  </si>
+  <si>
+    <t>User is logged in and has multiple products in cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proceed to checkout information page
+Enter valid customer information
+Click Continue
+Capture item prices, item total, tax, and total</t>
+  </si>
+  <si>
+    <t>Item total should equal sum of item prices, total should equal item total plus tax, and all selected items should be displayed</t>
+  </si>
+  <si>
+    <t>Use data-test selectors: inventory-item-price, subtotal-label, tax-label, total-label</t>
+  </si>
+  <si>
+    <t>CheckoutOverviewPage</t>
+  </si>
+  <si>
+    <t>TC_CHECKOUT_004</t>
+  </si>
+  <si>
+    <t>Cancel checkout from information page</t>
+  </si>
+  <si>
+    <t>User is on checkout information page</t>
+  </si>
+  <si>
+    <t>Click Cancel</t>
+  </si>
+  <si>
+    <t>User should be returned to the cart page</t>
+  </si>
+  <si>
+    <t>Use data-test selector: cancel</t>
+  </si>
+  <si>
+    <t>TC_CHECKOUT_005</t>
+  </si>
+  <si>
+    <t>Cancel checkout from overview page</t>
+  </si>
+  <si>
+    <t>User is on checkout overview page</t>
+  </si>
+  <si>
+    <t>User should be returned to the inventory page and cart contents should remain available</t>
+  </si>
+  <si>
+    <t>Use data-test selector: cancel and shopping-cart-badge</t>
+  </si>
+  <si>
+    <t>TC_CHECKOUT_006</t>
+  </si>
+  <si>
+    <t>Return to products after order completion</t>
+  </si>
+  <si>
+    <t>User has completed checkout and is on checkout complete page</t>
+  </si>
+  <si>
+    <t>Click Back Home</t>
+  </si>
+  <si>
+    <t>Use data-test selector: back-to-products</t>
+  </si>
+  <si>
+    <t>CheckoutCompletePage</t>
+  </si>
+  <si>
+    <t>TC_CHECKOUT_007</t>
+  </si>
+  <si>
+    <t>Attempt checkout with empty cart</t>
+  </si>
+  <si>
+    <t>Application should prevent checkout for an empty cart or handle it consistently without allowing an invalid order</t>
+  </si>
+  <si>
+    <t>Use data-test selector: checkout and validate resulting page state</t>
+  </si>
+  <si>
+    <t>TC_ERROR_001</t>
+  </si>
+  <si>
+    <t>Error validation</t>
+  </si>
+  <si>
+    <t>Checkout information validation when first name is empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leave first name field empty
 Enter last name Doe
 Enter postal code 12345
 Click Continue</t>
   </si>
   <si>
-    <t>User should be redirected to checkout overview page</t>
-  </si>
-  <si>
-    <t>Use data-test selectors firstName, lastName, postalCode, continue, and title</t>
-  </si>
-  <si>
-    <t>TC_CHECKOUT_003</t>
-  </si>
-  <si>
-    <t>Cancel checkout from checkout information page</t>
-  </si>
-  <si>
-    <t>User is logged in and is on checkout step one</t>
-  </si>
-  <si>
-    <t>Click Cancel</t>
-  </si>
-  <si>
-    <t>User should be redirected back to the cart page</t>
-  </si>
-  <si>
-    <t>Use data-test selector cancel and title</t>
-  </si>
-  <si>
-    <t>TC_CHECKOUT_004</t>
-  </si>
-  <si>
-    <t>Cancel checkout from checkout overview page</t>
-  </si>
-  <si>
-    <t>User is logged in and is on checkout overview page</t>
-  </si>
-  <si>
-    <t>User should be redirected back to the inventory page</t>
-  </si>
-  <si>
-    <t>CheckoutOverviewPage</t>
-  </si>
-  <si>
-    <t>TC_CHECKOUT_005</t>
-  </si>
-  <si>
-    <t>Verify checkout overview item total and tax calculation</t>
-  </si>
-  <si>
-    <t>User is logged in, has multiple items in cart, and is on checkout overview page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capture prices of all cart items displayed on checkout overview
-Calculate item total
-Calculate tax
-Compare calculated values with displayed Item total, Tax, and Total</t>
-  </si>
-  <si>
-    <t>Displayed item total should equal sum of item prices, tax should be calculated correctly, and total should equal item total plus tax</t>
-  </si>
-  <si>
-    <t>Use data-test selectors inventory-item-price, subtotal-label, tax-label, and total-label</t>
-  </si>
-  <si>
-    <t>TC_CHECKOUT_006</t>
-  </si>
-  <si>
-    <t>Return to home after order completion</t>
-  </si>
-  <si>
-    <t>User completed checkout and is on checkout complete page</t>
-  </si>
-  <si>
-    <t>Click Back Home</t>
-  </si>
-  <si>
-    <t>User should be redirected to inventory page and cart should be empty</t>
-  </si>
-  <si>
-    <t>Use data-test selectors back-to-products, title, and shopping-cart-badge</t>
-  </si>
-  <si>
-    <t>CheckoutCompletePage</t>
-  </si>
-  <si>
-    <t>TC_ERROR_001</t>
-  </si>
-  <si>
-    <t>Error validation</t>
-  </si>
-  <si>
-    <t>Checkout with blank first name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leave first name blank
-Enter last name Doe
+    <t>User should remain on checkout information page and an error message should indicate first name is required</t>
+  </si>
+  <si>
+    <t>Use data-test selectors: firstName, lastName, postalCode, continue, error</t>
+  </si>
+  <si>
+    <t>TC_ERROR_002</t>
+  </si>
+  <si>
+    <t>Checkout information validation when last name is empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter first name John
+Leave last name field empty
 Enter postal code 12345
 Click Continue</t>
   </si>
   <si>
-    <t>User should remain on checkout step one and error message 'Error: First Name is required' should be displayed</t>
-  </si>
-  <si>
-    <t>Use data-test selectors firstName, lastName, postalCode, continue, and error</t>
-  </si>
-  <si>
-    <t>TC_ERROR_002</t>
-  </si>
-  <si>
-    <t>Checkout with blank last name</t>
+    <t>User should remain on checkout information page and an error message should indicate last name is required</t>
+  </si>
+  <si>
+    <t>TC_ERROR_003</t>
+  </si>
+  <si>
+    <t>Checkout information validation when postal code is empty</t>
   </si>
   <si>
     <t xml:space="preserve">Enter first name John
-Leave last name blank
+Enter last name Doe
+Leave postal code field empty
+Click Continue</t>
+  </si>
+  <si>
+    <t>User should remain on checkout information page and an error message should indicate postal code is required</t>
+  </si>
+  <si>
+    <t>TC_ERROR_004</t>
+  </si>
+  <si>
+    <t>Dismiss login error message</t>
+  </si>
+  <si>
+    <t>Login error message is displayed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trigger a login validation error
+Click the error close button</t>
+  </si>
+  <si>
+    <t>Error message should be dismissed from the login page</t>
+  </si>
+  <si>
+    <t>Use data-test selector: error-button</t>
+  </si>
+  <si>
+    <t>TC_ERROR_005</t>
+  </si>
+  <si>
+    <t>Direct access to cart page without login</t>
+  </si>
+  <si>
+    <t>User is not authenticated</t>
+  </si>
+  <si>
+    <t>Navigate directly to https://www.saucedemo.com/cart.html</t>
+  </si>
+  <si>
+    <t>User should be redirected to login page and an error message should indicate access requires login</t>
+  </si>
+  <si>
+    <t>TC_ERROR_006</t>
+  </si>
+  <si>
+    <t>Direct access to checkout step one without login</t>
+  </si>
+  <si>
+    <t>Navigate directly to https://www.saucedemo.com/checkout-step-one.html</t>
+  </si>
+  <si>
+    <t>TC_ERROR_007</t>
+  </si>
+  <si>
+    <t>Checkout form accepts special characters in name fields</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter first name with special characters
+Enter last name with special characters
 Enter postal code 12345
 Click Continue</t>
   </si>
   <si>
-    <t>User should remain on checkout step one and error message 'Error: Last Name is required' should be displayed</t>
-  </si>
-  <si>
-    <t>TC_ERROR_003</t>
-  </si>
-  <si>
-    <t>Checkout with blank postal code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enter first name John
-Enter last name Doe
-Leave postal code blank
+    <t>Application should handle special characters safely without crashing or rendering invalid markup</t>
+  </si>
+  <si>
+    <t>Use data-test selectors: firstName, lastName, postalCode, continue</t>
+  </si>
+  <si>
+    <t>TC_ERROR_008</t>
+  </si>
+  <si>
+    <t>Checkout form accepts very long input values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter very long first name value
+Enter very long last name value
+Enter very long postal code value
 Click Continue</t>
   </si>
   <si>
-    <t>User should remain on checkout step one and error message 'Error: Postal Code is required' should be displayed</t>
-  </si>
-  <si>
-    <t>TC_ERROR_004</t>
-  </si>
-  <si>
-    <t>Dismiss checkout validation error</t>
-  </si>
-  <si>
-    <t>User is on checkout step one and validation error is displayed</t>
-  </si>
-  <si>
-    <t>Click the error close button</t>
-  </si>
-  <si>
-    <t>Validation error message should be dismissed</t>
-  </si>
-  <si>
-    <t>Use data-test selector error-button</t>
-  </si>
-  <si>
-    <t>TC_ERROR_005</t>
-  </si>
-  <si>
-    <t>Checkout with whitespace-only first name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enter spaces in first name field
-Enter last name Doe
-Enter postal code 12345
-Click Continue</t>
-  </si>
-  <si>
-    <t>Application should validate trimmed input; ideally whitespace-only first name should be rejected with first name required error</t>
-  </si>
-  <si>
-    <t>TC_ERROR_006</t>
-  </si>
-  <si>
-    <t>Checkout with very long customer information values</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enter a very long string in first name field
-Enter a very long string in last name field
-Enter a very long string in postal code field
-Click Continue</t>
-  </si>
-  <si>
-    <t>Application should handle long input without UI breakage, crash, or script execution</t>
-  </si>
-  <si>
-    <t>TC_ERROR_007</t>
-  </si>
-  <si>
-    <t>Checkout fields with special characters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enter special characters in first name field
-Enter special characters in last name field
-Enter special characters in postal code field
-Click Continue</t>
-  </si>
-  <si>
-    <t>Application should handle special characters safely without crashing or rendering executable content</t>
+    <t>Application should remain stable and either accept or validate long values without layout breakage or crash</t>
   </si>
   <si>
     <t>TC_ACCESSIBILITY_001</t>
@@ -810,193 +781,200 @@
     <t>Accessibility</t>
   </si>
   <si>
-    <t>Login page supports keyboard-only navigation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use Tab key to navigate through username field, password field, and Login button
-Use Shift+Tab to navigate backward
-Press Enter on Login button after entering valid credentials</t>
-  </si>
-  <si>
-    <t>All interactive elements should be reachable in logical order and login should be possible using keyboard only</t>
-  </si>
-  <si>
-    <t>Use keyboard events and validate focus using data-test selectors username, password, and login-button</t>
+    <t>Verify login page form fields have accessible names</t>
+  </si>
+  <si>
+    <t>User is on login page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run accessibility scan on login page
+Inspect username and password fields
+Inspect login button</t>
+  </si>
+  <si>
+    <t>Username field, password field, and login button should have clear accessible names and no critical accessibility violations</t>
+  </si>
+  <si>
+    <t>Use accessibility roles and labels where available, plus data-test selectors for fallback</t>
   </si>
   <si>
     <t>TC_ACCESSIBILITY_002</t>
   </si>
   <si>
-    <t>Inventory page supports keyboard-only navigation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use Tab key to navigate through menu button, cart link, sort dropdown, product links, and Add to cart buttons
-Activate controls using Enter or Space</t>
-  </si>
-  <si>
-    <t>All interactive inventory page elements should be keyboard accessible and visible focus should be present</t>
-  </si>
-  <si>
-    <t>Use keyboard events and validate activeElement against data-test selectors</t>
+    <t>Verify keyboard-only login flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use Tab key to focus username field
+Enter username standard_user
+Tab to password field
+Enter password secret_sauce
+Tab to Login button
+Press Enter</t>
+  </si>
+  <si>
+    <t>User should be able to complete login using only the keyboard</t>
+  </si>
+  <si>
+    <t>Use keyboard actions and verify focus order with activeElement</t>
   </si>
   <si>
     <t>TC_ACCESSIBILITY_003</t>
   </si>
   <si>
-    <t>Cart and checkout pages support keyboard-only navigation</t>
+    <t>Verify visible focus indicators on interactive elements</t>
+  </si>
+  <si>
+    <t>User is on inventory page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navigate through page using Tab key
+Observe focus state for menu button, cart link, sort dropdown, product links, and Add to cart buttons</t>
+  </si>
+  <si>
+    <t>All interactive elements should receive keyboard focus in a logical order and show a visible focus indicator</t>
+  </si>
+  <si>
+    <t>Partial</t>
+  </si>
+  <si>
+    <t>Use keyboard navigation, CSS focus state checks, and visual validation</t>
+  </si>
+  <si>
+    <t>TC_ACCESSIBILITY_004</t>
+  </si>
+  <si>
+    <t>Verify inventory product images have accessible alternatives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inspect all product images
+Verify each image has an alt attribute or is appropriately hidden if decorative</t>
+  </si>
+  <si>
+    <t>Each product image should have meaningful alternative text or be marked decorative if it does not convey important information</t>
+  </si>
+  <si>
+    <t>Use image elements within inventory-item containers</t>
+  </si>
+  <si>
+    <t>TC_ACCESSIBILITY_005</t>
+  </si>
+  <si>
+    <t>Verify color contrast on login and inventory pages</t>
+  </si>
+  <si>
+    <t>User can access login and inventory pages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run automated accessibility scan on login page
+Log in and run automated accessibility scan on inventory page
+Review color contrast findings</t>
+  </si>
+  <si>
+    <t>Text and meaningful UI components should meet WCAG AA contrast requirements</t>
+  </si>
+  <si>
+    <t>Use axe-core or equivalent accessibility scanning library</t>
+  </si>
+  <si>
+    <t>AccessibilityScan</t>
+  </si>
+  <si>
+    <t>TC_ACCESSIBILITY_006</t>
+  </si>
+  <si>
+    <t>Verify cart and checkout pages support keyboard navigation</t>
   </si>
   <si>
     <t xml:space="preserve">Navigate to cart using keyboard
-Activate Checkout using keyboard
-Complete checkout form using keyboard
-Activate Continue and Finish using keyboard</t>
-  </si>
-  <si>
-    <t>Cart and checkout flow should be completable without a mouse</t>
-  </si>
-  <si>
-    <t>Use keyboard events with data-test selectors shopping-cart-link, checkout, firstName, lastName, postalCode, continue, and finish</t>
-  </si>
-  <si>
-    <t>TC_ACCESSIBILITY_004</t>
-  </si>
-  <si>
-    <t>Form inputs have accessible names</t>
-  </si>
-  <si>
-    <t>User is on login page or checkout step one page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inspect username and password inputs on login page
-Inspect first name, last name, and postal code inputs on checkout page</t>
-  </si>
-  <si>
-    <t>All form inputs should have accessible names through labels, aria-label, placeholder, or equivalent accessible text</t>
-  </si>
-  <si>
-    <t>Use accessibility queries by role and name where possible, or validate computed accessible names</t>
-  </si>
-  <si>
-    <t>TC_ACCESSIBILITY_005</t>
-  </si>
-  <si>
-    <t>Error messages are perceivable by assistive technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trigger a validation error
-Inspect the error message element
-Verify focus handling after error</t>
-  </si>
-  <si>
-    <t>Error message should be visible, programmatically determinable, and focus should remain in a logical location for correction</t>
-  </si>
-  <si>
-    <t>Partial</t>
-  </si>
-  <si>
-    <t>Use data-test selector error and supplement automation with screen reader or accessibility tree validation</t>
-  </si>
-  <si>
-    <t>TC_ACCESSIBILITY_006</t>
-  </si>
-  <si>
-    <t>Images have meaningful alternative text or are marked decorative</t>
-  </si>
-  <si>
-    <t>User is logged in and inventory page is displayed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inspect all product images on inventory page
-Inspect product image on product detail page</t>
-  </si>
-  <si>
-    <t>Product images should have meaningful alt text matching or describing the product, or be appropriately marked decorative if not informative</t>
-  </si>
-  <si>
-    <t>Use image elements within inventory-item and validate alt attributes</t>
+Proceed to checkout using keyboard
+Enter customer information using keyboard
+Continue to overview and finish checkout using keyboard</t>
+  </si>
+  <si>
+    <t>User should be able to complete cart and checkout flow using keyboard only</t>
+  </si>
+  <si>
+    <t>Use keyboard actions and activeElement assertions</t>
   </si>
   <si>
     <t>TC_ACCESSIBILITY_007</t>
   </si>
   <si>
-    <t>Page headings and landmarks are structured correctly</t>
-  </si>
-  <si>
-    <t>User navigates through login, inventory, cart, and checkout pages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inspect heading structure on each page
-Verify page title or main heading describes the current page</t>
-  </si>
-  <si>
-    <t>Each page should have a meaningful heading and a logical structure to help screen reader users understand context</t>
-  </si>
-  <si>
-    <t>Use role-based selectors for headings and data-test selector title</t>
-  </si>
-  <si>
-    <t>BasePage</t>
+    <t>Verify error messages are perceivable by assistive technologies</t>
+  </si>
+  <si>
+    <t>User is on login page or checkout information page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trigger a required field validation error
+Inspect error message container and associated fields</t>
+  </si>
+  <si>
+    <t>Error message should be visible, descriptive, programmatically determinable, and associated with the relevant form field where applicable</t>
+  </si>
+  <si>
+    <t>Use data-test selector: error and inspect ARIA attributes</t>
+  </si>
+  <si>
+    <t>ValidationPage</t>
   </si>
   <si>
     <t>TC_ACCESSIBILITY_008</t>
   </si>
   <si>
-    <t>Color contrast meets WCAG requirements</t>
+    <t>Verify page landmarks and headings</t>
   </si>
   <si>
     <t>User can access login, inventory, cart, and checkout pages</t>
   </si>
   <si>
-    <t xml:space="preserve">Run automated accessibility scan on key pages
-Check text, buttons, links, and error messages for contrast</t>
-  </si>
-  <si>
-    <t>Text and UI controls should meet WCAG 2.1 AA contrast requirements</t>
-  </si>
-  <si>
-    <t>Use automated accessibility tooling such as axe-core and manually verify flagged contrast issues</t>
+    <t xml:space="preserve">Run accessibility scan on major pages
+Inspect heading structure
+Inspect landmark regions</t>
+  </si>
+  <si>
+    <t>Pages should have meaningful headings and landmark structure to support screen reader navigation</t>
+  </si>
+  <si>
+    <t>Use accessibility tree inspection and axe-core checks</t>
   </si>
   <si>
     <t>TC_ACCESSIBILITY_009</t>
   </si>
   <si>
-    <t>Visible focus indicator is present for interactive elements</t>
-  </si>
-  <si>
-    <t>User is on login, inventory, cart, or checkout page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navigate through interactive elements using Tab
-Observe focus indication on each focused element</t>
-  </si>
-  <si>
-    <t>Every focused interactive element should display a clear visible focus indicator</t>
-  </si>
-  <si>
-    <t>Use keyboard events and visual assertion or manual review for focus styling</t>
+    <t>Verify responsive zoom at 200 percent</t>
+  </si>
+  <si>
+    <t>User can access application pages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set browser zoom to 200 percent
+Navigate login, inventory, cart, and checkout pages
+Check for clipped text, overlapping controls, and horizontal scrolling</t>
+  </si>
+  <si>
+    <t>Content should remain readable and usable at 200 percent zoom without loss of functionality</t>
+  </si>
+  <si>
+    <t>Use viewport and visual regression checks</t>
   </si>
   <si>
     <t>TC_ACCESSIBILITY_010</t>
   </si>
   <si>
-    <t>Automated axe accessibility scan on critical pages</t>
-  </si>
-  <si>
-    <t>User can access login, inventory, cart, checkout information, checkout overview, and checkout complete pages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Run axe-core scan on login page
-Log in and run axe-core scan on inventory page
-Add item to cart and run axe-core scan on cart page
-Run axe-core scan on checkout information page
-Run axe-core scan on checkout overview page
-Complete order and run axe-core scan on checkout complete page</t>
-  </si>
-  <si>
-    <t>No critical or serious accessibility violations should be detected on critical pages</t>
-  </si>
-  <si>
-    <t>Use page-level axe-core scans and data-test selectors for navigation setup</t>
+    <t>Verify menu can be opened and closed with keyboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tab to burger menu button
+Press Enter or Space to open menu
+Navigate menu links using keyboard
+Activate close button using keyboard</t>
+  </si>
+  <si>
+    <t>Menu should be fully operable by keyboard, focus should move logically, and menu should close when requested</t>
+  </si>
+  <si>
+    <t>Use data-test selectors: open-menu, close-menu, inventory-sidebar-link, logout-sidebar-link</t>
   </si>
 </sst>
 </file>
@@ -1373,7 +1351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
@@ -1551,7 +1529,7 @@
         <v>34</v>
       </c>
       <c r="H5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I5" t="s">
         <v>19</v>
@@ -1565,13 +1543,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
         <v>24</v>
@@ -1583,16 +1561,16 @@
         <v>16</v>
       </c>
       <c r="G6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" t="s">
         <v>38</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" t="s">
         <v>39</v>
-      </c>
-      <c r="I6" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" t="s">
-        <v>40</v>
       </c>
       <c r="K6" t="s">
         <v>21</v>
@@ -1600,13 +1578,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
         <v>24</v>
@@ -1618,16 +1596,16 @@
         <v>16</v>
       </c>
       <c r="G7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" t="s">
         <v>43</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" t="s">
         <v>44</v>
-      </c>
-      <c r="I7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" t="s">
-        <v>45</v>
       </c>
       <c r="K7" t="s">
         <v>21</v>
@@ -1635,34 +1613,34 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" t="s">
         <v>47</v>
       </c>
-      <c r="D8" t="s">
-        <v>24</v>
-      </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
       </c>
       <c r="G8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H8" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="I8" t="s">
         <v>19</v>
       </c>
       <c r="J8" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="K8" t="s">
         <v>21</v>
@@ -1670,19 +1648,19 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="F9" t="s">
         <v>53</v>
@@ -1700,97 +1678,97 @@
         <v>56</v>
       </c>
       <c r="K9" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I10" t="s">
         <v>19</v>
       </c>
       <c r="J10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K10" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I11" t="s">
         <v>19</v>
       </c>
       <c r="J11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K11" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="E12" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="G12" t="s">
         <v>73</v>
@@ -1802,18 +1780,18 @@
         <v>19</v>
       </c>
       <c r="J12" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="K12" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
         <v>77</v>
@@ -1822,433 +1800,433 @@
         <v>14</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F13" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" t="s">
         <v>78</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>79</v>
       </c>
-      <c r="H13" t="s">
-        <v>80</v>
-      </c>
       <c r="I13" t="s">
         <v>19</v>
       </c>
       <c r="J13" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="K13" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
         <v>14</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F14" t="s">
+        <v>67</v>
+      </c>
+      <c r="G14" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" t="s">
+        <v>83</v>
+      </c>
+      <c r="I14" t="s">
+        <v>19</v>
+      </c>
+      <c r="J14" t="s">
         <v>84</v>
       </c>
-      <c r="G14" t="s">
-        <v>85</v>
-      </c>
-      <c r="H14" t="s">
-        <v>86</v>
-      </c>
-      <c r="I14" t="s">
-        <v>19</v>
-      </c>
-      <c r="J14" t="s">
-        <v>87</v>
-      </c>
       <c r="K14" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
         <v>14</v>
       </c>
       <c r="E15" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F15" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="G15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I15" t="s">
         <v>19</v>
       </c>
       <c r="J15" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="K15" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
         <v>14</v>
       </c>
       <c r="E16" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F16" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="G16" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="H16" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="I16" t="s">
         <v>19</v>
       </c>
       <c r="J16" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="K16" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
         <v>14</v>
       </c>
       <c r="E17" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="F17" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="G17" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H17" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="I17" t="s">
         <v>19</v>
       </c>
       <c r="J17" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="K17" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
         <v>14</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="F18" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="G18" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H18" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="I18" t="s">
         <v>19</v>
       </c>
       <c r="J18" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="K18" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" t="s">
+        <v>108</v>
+      </c>
+      <c r="G19" t="s">
+        <v>109</v>
+      </c>
+      <c r="H19" t="s">
+        <v>110</v>
+      </c>
+      <c r="I19" t="s">
+        <v>19</v>
+      </c>
+      <c r="J19" t="s">
         <v>111</v>
       </c>
-      <c r="B19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" t="s">
-        <v>112</v>
-      </c>
-      <c r="D19" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" t="s">
-        <v>52</v>
-      </c>
-      <c r="F19" t="s">
-        <v>78</v>
-      </c>
-      <c r="G19" t="s">
-        <v>113</v>
-      </c>
-      <c r="H19" t="s">
-        <v>114</v>
-      </c>
-      <c r="I19" t="s">
-        <v>19</v>
-      </c>
-      <c r="J19" t="s">
-        <v>110</v>
-      </c>
       <c r="K19" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="C20" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D20" t="s">
         <v>14</v>
       </c>
       <c r="E20" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="F20" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="G20" t="s">
+        <v>115</v>
+      </c>
+      <c r="H20" t="s">
+        <v>116</v>
+      </c>
+      <c r="I20" t="s">
+        <v>19</v>
+      </c>
+      <c r="J20" t="s">
         <v>117</v>
       </c>
-      <c r="H20" t="s">
-        <v>118</v>
-      </c>
-      <c r="I20" t="s">
-        <v>19</v>
-      </c>
-      <c r="J20" t="s">
-        <v>119</v>
-      </c>
       <c r="K20" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="C21" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D21" t="s">
         <v>14</v>
       </c>
       <c r="E21" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="F21" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="G21" t="s">
+        <v>121</v>
+      </c>
+      <c r="H21" t="s">
         <v>122</v>
       </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J21" t="s">
         <v>123</v>
       </c>
-      <c r="I21" t="s">
-        <v>19</v>
-      </c>
-      <c r="J21" t="s">
-        <v>119</v>
-      </c>
       <c r="K21" t="s">
-        <v>69</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D22" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
       </c>
       <c r="F22" t="s">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="G22" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H22" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I22" t="s">
         <v>19</v>
       </c>
       <c r="J22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K22" t="s">
-        <v>69</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="C23" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D23" t="s">
         <v>14</v>
       </c>
       <c r="E23" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="F23" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G23" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H23" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I23" t="s">
         <v>19</v>
       </c>
       <c r="J23" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K23" t="s">
-        <v>69</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B24" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="C24" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D24" t="s">
         <v>14</v>
       </c>
       <c r="E24" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F24" t="s">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="G24" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H24" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I24" t="s">
         <v>19</v>
       </c>
       <c r="J24" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K24" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B25" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="C25" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D25" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="E25" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F25" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G25" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="H25" t="s">
         <v>146</v>
@@ -2260,7 +2238,7 @@
         <v>147</v>
       </c>
       <c r="K25" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -2268,16 +2246,16 @@
         <v>148</v>
       </c>
       <c r="B26" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="C26" t="s">
         <v>149</v>
       </c>
       <c r="D26" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="E26" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F26" t="s">
         <v>150</v>
@@ -2295,7 +2273,7 @@
         <v>153</v>
       </c>
       <c r="K26" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -2303,19 +2281,19 @@
         <v>154</v>
       </c>
       <c r="B27" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="C27" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D27" t="s">
         <v>14</v>
       </c>
       <c r="E27" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="F27" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="G27" t="s">
         <v>157</v>
@@ -2330,7 +2308,7 @@
         <v>159</v>
       </c>
       <c r="K27" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -2338,7 +2316,7 @@
         <v>160</v>
       </c>
       <c r="B28" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="C28" t="s">
         <v>161</v>
@@ -2350,22 +2328,22 @@
         <v>15</v>
       </c>
       <c r="F28" t="s">
+        <v>133</v>
+      </c>
+      <c r="G28" t="s">
         <v>162</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>163</v>
       </c>
-      <c r="H28" t="s">
+      <c r="I28" t="s">
+        <v>19</v>
+      </c>
+      <c r="J28" t="s">
         <v>164</v>
       </c>
-      <c r="I28" t="s">
-        <v>19</v>
-      </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
         <v>165</v>
-      </c>
-      <c r="K28" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -2373,69 +2351,69 @@
         <v>166</v>
       </c>
       <c r="B29" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="C29" t="s">
         <v>167</v>
       </c>
       <c r="D29" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="E29" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="F29" t="s">
         <v>168</v>
       </c>
       <c r="G29" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H29" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I29" t="s">
         <v>19</v>
       </c>
       <c r="J29" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K29" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B30" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="C30" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D30" t="s">
         <v>14</v>
       </c>
       <c r="E30" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G30" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H30" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I30" t="s">
         <v>19</v>
       </c>
       <c r="J30" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K30" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -2443,7 +2421,7 @@
         <v>179</v>
       </c>
       <c r="B31" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="C31" t="s">
         <v>180</v>
@@ -2452,176 +2430,176 @@
         <v>14</v>
       </c>
       <c r="E31" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F31" t="s">
         <v>181</v>
       </c>
       <c r="G31" t="s">
+        <v>176</v>
+      </c>
+      <c r="H31" t="s">
         <v>182</v>
       </c>
-      <c r="H31" t="s">
+      <c r="I31" t="s">
+        <v>19</v>
+      </c>
+      <c r="J31" t="s">
         <v>183</v>
       </c>
-      <c r="I31" t="s">
-        <v>19</v>
-      </c>
-      <c r="J31" t="s">
-        <v>184</v>
-      </c>
       <c r="K31" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>184</v>
+      </c>
+      <c r="B32" t="s">
+        <v>155</v>
+      </c>
+      <c r="C32" t="s">
         <v>185</v>
-      </c>
-      <c r="B32" t="s">
-        <v>172</v>
-      </c>
-      <c r="C32" t="s">
-        <v>186</v>
       </c>
       <c r="D32" t="s">
         <v>14</v>
       </c>
       <c r="E32" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F32" t="s">
+        <v>186</v>
+      </c>
+      <c r="G32" t="s">
         <v>187</v>
       </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
+        <v>141</v>
+      </c>
+      <c r="I32" t="s">
+        <v>19</v>
+      </c>
+      <c r="J32" t="s">
         <v>188</v>
       </c>
-      <c r="H32" t="s">
+      <c r="K32" t="s">
         <v>189</v>
-      </c>
-      <c r="I32" t="s">
-        <v>19</v>
-      </c>
-      <c r="J32" t="s">
-        <v>190</v>
-      </c>
-      <c r="K32" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>190</v>
+      </c>
+      <c r="B33" t="s">
+        <v>155</v>
+      </c>
+      <c r="C33" t="s">
         <v>191</v>
       </c>
-      <c r="B33" t="s">
-        <v>172</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
+        <v>47</v>
+      </c>
+      <c r="E33" t="s">
+        <v>48</v>
+      </c>
+      <c r="F33" t="s">
+        <v>145</v>
+      </c>
+      <c r="G33" t="s">
+        <v>157</v>
+      </c>
+      <c r="H33" t="s">
         <v>192</v>
       </c>
-      <c r="D33" t="s">
-        <v>14</v>
-      </c>
-      <c r="E33" t="s">
-        <v>52</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="I33" t="s">
+        <v>19</v>
+      </c>
+      <c r="J33" t="s">
         <v>193</v>
       </c>
-      <c r="G33" t="s">
-        <v>188</v>
-      </c>
-      <c r="H33" t="s">
-        <v>194</v>
-      </c>
-      <c r="I33" t="s">
-        <v>19</v>
-      </c>
-      <c r="J33" t="s">
-        <v>190</v>
-      </c>
       <c r="K33" t="s">
-        <v>195</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>194</v>
+      </c>
+      <c r="B34" t="s">
+        <v>195</v>
+      </c>
+      <c r="C34" t="s">
         <v>196</v>
       </c>
-      <c r="B34" t="s">
-        <v>172</v>
-      </c>
-      <c r="C34" t="s">
-        <v>197</v>
-      </c>
       <c r="D34" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
       </c>
       <c r="F34" t="s">
+        <v>175</v>
+      </c>
+      <c r="G34" t="s">
+        <v>197</v>
+      </c>
+      <c r="H34" t="s">
         <v>198</v>
       </c>
-      <c r="G34" t="s">
+      <c r="I34" t="s">
+        <v>19</v>
+      </c>
+      <c r="J34" t="s">
         <v>199</v>
       </c>
-      <c r="H34" t="s">
-        <v>200</v>
-      </c>
-      <c r="I34" t="s">
-        <v>19</v>
-      </c>
-      <c r="J34" t="s">
-        <v>201</v>
-      </c>
       <c r="K34" t="s">
-        <v>195</v>
+        <v>165</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>200</v>
+      </c>
+      <c r="B35" t="s">
+        <v>195</v>
+      </c>
+      <c r="C35" t="s">
+        <v>201</v>
+      </c>
+      <c r="D35" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35" t="s">
+        <v>175</v>
+      </c>
+      <c r="G35" t="s">
         <v>202</v>
       </c>
-      <c r="B35" t="s">
-        <v>172</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="H35" t="s">
         <v>203</v>
       </c>
-      <c r="D35" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" t="s">
-        <v>52</v>
-      </c>
-      <c r="F35" t="s">
-        <v>204</v>
-      </c>
-      <c r="G35" t="s">
-        <v>205</v>
-      </c>
-      <c r="H35" t="s">
-        <v>206</v>
-      </c>
       <c r="I35" t="s">
         <v>19</v>
       </c>
       <c r="J35" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="K35" t="s">
-        <v>208</v>
+        <v>165</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B36" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="C36" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D36" t="s">
         <v>24</v>
@@ -2630,68 +2608,68 @@
         <v>15</v>
       </c>
       <c r="F36" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="G36" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="H36" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="I36" t="s">
         <v>19</v>
       </c>
       <c r="J36" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="K36" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="B37" t="s">
+        <v>195</v>
+      </c>
+      <c r="C37" t="s">
+        <v>209</v>
+      </c>
+      <c r="D37" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" t="s">
+        <v>48</v>
+      </c>
+      <c r="F37" t="s">
         <v>210</v>
       </c>
-      <c r="C37" t="s">
-        <v>216</v>
-      </c>
-      <c r="D37" t="s">
-        <v>24</v>
-      </c>
-      <c r="E37" t="s">
-        <v>15</v>
-      </c>
-      <c r="F37" t="s">
-        <v>181</v>
-      </c>
       <c r="G37" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="H37" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="I37" t="s">
         <v>19</v>
       </c>
       <c r="J37" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K37" t="s">
-        <v>178</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B38" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="C38" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D38" t="s">
         <v>24</v>
@@ -2700,194 +2678,194 @@
         <v>15</v>
       </c>
       <c r="F38" t="s">
-        <v>181</v>
+        <v>216</v>
       </c>
       <c r="G38" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="H38" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="I38" t="s">
         <v>19</v>
       </c>
       <c r="J38" t="s">
-        <v>214</v>
+        <v>111</v>
       </c>
       <c r="K38" t="s">
-        <v>178</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B39" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="C39" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D39" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E39" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="F39" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="G39" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H39" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="I39" t="s">
         <v>19</v>
       </c>
       <c r="J39" t="s">
-        <v>228</v>
+        <v>111</v>
       </c>
       <c r="K39" t="s">
-        <v>178</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="B40" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="C40" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="D40" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="E40" t="s">
-        <v>52</v>
+        <v>224</v>
       </c>
       <c r="F40" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="G40" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="H40" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="I40" t="s">
         <v>19</v>
       </c>
       <c r="J40" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="K40" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B41" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="C41" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D41" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="E41" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="F41" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="G41" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="H41" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="I41" t="s">
         <v>19</v>
       </c>
       <c r="J41" t="s">
-        <v>184</v>
+        <v>227</v>
       </c>
       <c r="K41" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>232</v>
+      </c>
+      <c r="B42" t="s">
+        <v>233</v>
+      </c>
+      <c r="C42" t="s">
+        <v>234</v>
+      </c>
+      <c r="D42" t="s">
+        <v>233</v>
+      </c>
+      <c r="E42" t="s">
+        <v>15</v>
+      </c>
+      <c r="F42" t="s">
+        <v>235</v>
+      </c>
+      <c r="G42" t="s">
+        <v>236</v>
+      </c>
+      <c r="H42" t="s">
+        <v>237</v>
+      </c>
+      <c r="I42" t="s">
+        <v>19</v>
+      </c>
+      <c r="J42" t="s">
         <v>238</v>
       </c>
-      <c r="B42" t="s">
-        <v>210</v>
-      </c>
-      <c r="C42" t="s">
-        <v>239</v>
-      </c>
-      <c r="D42" t="s">
-        <v>72</v>
-      </c>
-      <c r="E42" t="s">
-        <v>235</v>
-      </c>
-      <c r="F42" t="s">
-        <v>181</v>
-      </c>
-      <c r="G42" t="s">
-        <v>240</v>
-      </c>
-      <c r="H42" t="s">
-        <v>241</v>
-      </c>
-      <c r="I42" t="s">
-        <v>19</v>
-      </c>
-      <c r="J42" t="s">
-        <v>184</v>
-      </c>
       <c r="K42" t="s">
-        <v>178</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B43" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C43" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D43" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
       </c>
       <c r="F43" t="s">
-        <v>16</v>
+        <v>235</v>
       </c>
       <c r="G43" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="H43" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="I43" t="s">
         <v>19</v>
       </c>
       <c r="J43" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="K43" t="s">
         <v>21</v>
@@ -2895,317 +2873,282 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B44" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C44" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D44" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
       </c>
       <c r="F44" t="s">
-        <v>78</v>
+        <v>246</v>
       </c>
       <c r="G44" t="s">
+        <v>247</v>
+      </c>
+      <c r="H44" t="s">
+        <v>248</v>
+      </c>
+      <c r="I44" t="s">
+        <v>249</v>
+      </c>
+      <c r="J44" t="s">
         <v>250</v>
       </c>
-      <c r="H44" t="s">
-        <v>251</v>
-      </c>
-      <c r="I44" t="s">
-        <v>19</v>
-      </c>
-      <c r="J44" t="s">
-        <v>252</v>
-      </c>
       <c r="K44" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>251</v>
+      </c>
+      <c r="B45" t="s">
+        <v>233</v>
+      </c>
+      <c r="C45" t="s">
+        <v>252</v>
+      </c>
+      <c r="D45" t="s">
+        <v>233</v>
+      </c>
+      <c r="E45" t="s">
+        <v>48</v>
+      </c>
+      <c r="F45" t="s">
+        <v>67</v>
+      </c>
+      <c r="G45" t="s">
         <v>253</v>
       </c>
-      <c r="B45" t="s">
-        <v>243</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="H45" t="s">
         <v>254</v>
       </c>
-      <c r="D45" t="s">
-        <v>243</v>
-      </c>
-      <c r="E45" t="s">
-        <v>15</v>
-      </c>
-      <c r="F45" t="s">
-        <v>174</v>
-      </c>
-      <c r="G45" t="s">
+      <c r="I45" t="s">
+        <v>19</v>
+      </c>
+      <c r="J45" t="s">
         <v>255</v>
       </c>
-      <c r="H45" t="s">
-        <v>256</v>
-      </c>
-      <c r="I45" t="s">
-        <v>19</v>
-      </c>
-      <c r="J45" t="s">
-        <v>257</v>
-      </c>
       <c r="K45" t="s">
-        <v>178</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B46" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D46" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
       </c>
       <c r="F46" t="s">
+        <v>258</v>
+      </c>
+      <c r="G46" t="s">
+        <v>259</v>
+      </c>
+      <c r="H46" t="s">
         <v>260</v>
       </c>
-      <c r="G46" t="s">
+      <c r="I46" t="s">
+        <v>19</v>
+      </c>
+      <c r="J46" t="s">
         <v>261</v>
       </c>
-      <c r="H46" t="s">
+      <c r="K46" t="s">
         <v>262</v>
-      </c>
-      <c r="I46" t="s">
-        <v>19</v>
-      </c>
-      <c r="J46" t="s">
-        <v>263</v>
-      </c>
-      <c r="K46" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>263</v>
+      </c>
+      <c r="B47" t="s">
+        <v>233</v>
+      </c>
+      <c r="C47" t="s">
         <v>264</v>
       </c>
-      <c r="B47" t="s">
-        <v>243</v>
-      </c>
-      <c r="C47" t="s">
-        <v>265</v>
-      </c>
       <c r="D47" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
       </c>
       <c r="F47" t="s">
-        <v>260</v>
+        <v>133</v>
       </c>
       <c r="G47" t="s">
+        <v>265</v>
+      </c>
+      <c r="H47" t="s">
         <v>266</v>
       </c>
-      <c r="H47" t="s">
+      <c r="I47" t="s">
+        <v>19</v>
+      </c>
+      <c r="J47" t="s">
         <v>267</v>
       </c>
-      <c r="I47" t="s">
-        <v>268</v>
-      </c>
-      <c r="J47" t="s">
-        <v>269</v>
-      </c>
       <c r="K47" t="s">
-        <v>21</v>
+        <v>165</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>268</v>
+      </c>
+      <c r="B48" t="s">
+        <v>233</v>
+      </c>
+      <c r="C48" t="s">
+        <v>269</v>
+      </c>
+      <c r="D48" t="s">
+        <v>233</v>
+      </c>
+      <c r="E48" t="s">
+        <v>15</v>
+      </c>
+      <c r="F48" t="s">
         <v>270</v>
       </c>
-      <c r="B48" t="s">
-        <v>243</v>
-      </c>
-      <c r="C48" t="s">
+      <c r="G48" t="s">
         <v>271</v>
       </c>
-      <c r="D48" t="s">
-        <v>243</v>
-      </c>
-      <c r="E48" t="s">
-        <v>52</v>
-      </c>
-      <c r="F48" t="s">
+      <c r="H48" t="s">
         <v>272</v>
       </c>
-      <c r="G48" t="s">
+      <c r="I48" t="s">
+        <v>249</v>
+      </c>
+      <c r="J48" t="s">
         <v>273</v>
       </c>
-      <c r="H48" t="s">
+      <c r="K48" t="s">
         <v>274</v>
-      </c>
-      <c r="I48" t="s">
-        <v>19</v>
-      </c>
-      <c r="J48" t="s">
-        <v>275</v>
-      </c>
-      <c r="K48" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>275</v>
+      </c>
+      <c r="B49" t="s">
+        <v>233</v>
+      </c>
+      <c r="C49" t="s">
         <v>276</v>
       </c>
-      <c r="B49" t="s">
-        <v>243</v>
-      </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
+        <v>233</v>
+      </c>
+      <c r="E49" t="s">
+        <v>48</v>
+      </c>
+      <c r="F49" t="s">
         <v>277</v>
       </c>
-      <c r="D49" t="s">
-        <v>243</v>
-      </c>
-      <c r="E49" t="s">
-        <v>52</v>
-      </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>278</v>
       </c>
-      <c r="G49" t="s">
+      <c r="H49" t="s">
         <v>279</v>
       </c>
-      <c r="H49" t="s">
+      <c r="I49" t="s">
+        <v>249</v>
+      </c>
+      <c r="J49" t="s">
         <v>280</v>
       </c>
-      <c r="I49" t="s">
-        <v>268</v>
-      </c>
-      <c r="J49" t="s">
-        <v>281</v>
-      </c>
       <c r="K49" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>281</v>
+      </c>
+      <c r="B50" t="s">
+        <v>233</v>
+      </c>
+      <c r="C50" t="s">
+        <v>282</v>
+      </c>
+      <c r="D50" t="s">
+        <v>233</v>
+      </c>
+      <c r="E50" t="s">
+        <v>48</v>
+      </c>
+      <c r="F50" t="s">
         <v>283</v>
       </c>
-      <c r="B50" t="s">
-        <v>243</v>
-      </c>
-      <c r="C50" t="s">
+      <c r="G50" t="s">
         <v>284</v>
       </c>
-      <c r="D50" t="s">
-        <v>243</v>
-      </c>
-      <c r="E50" t="s">
-        <v>15</v>
-      </c>
-      <c r="F50" t="s">
+      <c r="H50" t="s">
         <v>285</v>
       </c>
-      <c r="G50" t="s">
+      <c r="I50" t="s">
+        <v>249</v>
+      </c>
+      <c r="J50" t="s">
         <v>286</v>
       </c>
-      <c r="H50" t="s">
-        <v>287</v>
-      </c>
-      <c r="I50" t="s">
-        <v>268</v>
-      </c>
-      <c r="J50" t="s">
-        <v>288</v>
-      </c>
       <c r="K50" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>287</v>
+      </c>
+      <c r="B51" t="s">
+        <v>233</v>
+      </c>
+      <c r="C51" t="s">
+        <v>288</v>
+      </c>
+      <c r="D51" t="s">
+        <v>233</v>
+      </c>
+      <c r="E51" t="s">
+        <v>48</v>
+      </c>
+      <c r="F51" t="s">
+        <v>67</v>
+      </c>
+      <c r="G51" t="s">
         <v>289</v>
       </c>
-      <c r="B51" t="s">
-        <v>243</v>
-      </c>
-      <c r="C51" t="s">
+      <c r="H51" t="s">
         <v>290</v>
       </c>
-      <c r="D51" t="s">
-        <v>243</v>
-      </c>
-      <c r="E51" t="s">
-        <v>15</v>
-      </c>
-      <c r="F51" t="s">
+      <c r="I51" t="s">
+        <v>19</v>
+      </c>
+      <c r="J51" t="s">
         <v>291</v>
       </c>
-      <c r="G51" t="s">
-        <v>292</v>
-      </c>
-      <c r="H51" t="s">
-        <v>293</v>
-      </c>
-      <c r="I51" t="s">
-        <v>268</v>
-      </c>
-      <c r="J51" t="s">
-        <v>294</v>
-      </c>
       <c r="K51" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>295</v>
-      </c>
-      <c r="B52" t="s">
-        <v>243</v>
-      </c>
-      <c r="C52" t="s">
-        <v>296</v>
-      </c>
-      <c r="D52" t="s">
-        <v>243</v>
-      </c>
-      <c r="E52" t="s">
-        <v>15</v>
-      </c>
-      <c r="F52" t="s">
-        <v>297</v>
-      </c>
-      <c r="G52" t="s">
-        <v>298</v>
-      </c>
-      <c r="H52" t="s">
-        <v>299</v>
-      </c>
-      <c r="I52" t="s">
-        <v>19</v>
-      </c>
-      <c r="J52" t="s">
-        <v>300</v>
-      </c>
-      <c r="K52" t="s">
-        <v>282</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
